--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0021.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0021.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Này, Rover! Đợi lâu lắm rồi mới thấy cậu đến!</t>
+          <t>Này, Vận Mệnh Giả! Đợi lâu lắm rồi mới thấy cậu đến!</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Dạo này quanh khu mỏ có nhiều chuyện kỳ lạ lắm. Ta nghĩ cậu chính là người có thể gỡ rối vụ này.</t>
+          <t>Dạo này quanh khu mỏ có nhiều chuyện kỳ lạ lắm. Tao nghĩ cậu chính là người có thể gỡ rối vụ này.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Ta không biết cậu đã nghe qua chưa, nhưng ở Kim Châu có một câu chuyện dân gian rất đặc biệt...</t>
+          <t>Tao không biết cậu đã nghe qua chưa, nhưng ở Jinzhou có một câu chuyện dân gian rất đặc biệt...</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Thỏa thuận! Ta sẽ trả bất cứ giá nào để được tiếp tục rùng mình. Ta nóng lòng muốn ngươi khám phá ra sự thật!</t>
+          <t>Thỏa thuận! Tao sẽ trả bất cứ giá nào để được tiếp tục rùng mình. Tao nóng lòng muốn mày khám phá ra sự thật!</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Ngươi là thằng nào?! Dám lao vào đây... Coi thường dân Lưu Đày chúng ta à?!</t>
+          <t>Mày là thằng nào?! Dám lao vào đây... Coi thường dân Lưu Đày chúng tao à?!</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Cậu tưởng cậu là ai chứ?! Không cần phải nói cho cậu biết đâu!</t>
+          <t>Mày tưởng mày là ai chứ?! Không cần phải nói cho mày biết đâu!</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Về Mingyan à... Lính của ta trả lời cậu đủ rồi chứ? Đó là tất cả những gì chúng ta biết về cô ta, ta thề đấy. Cậu còn muốn gì nữa?</t>
+          <t>Về Mingyan à... Lính của tao trả lời cậu đủ rồi chứ? Đó là tất cả những gì chúng tao biết về cô ta, tao thề đấy. Cậu còn muốn gì nữa?</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Gì? Cậu không thấy là chúng ta không phải đối thủ của {Male=hắn;Female=cô ta} à? Muốn gây sự thì cứ tự nhiên, nhưng tôi không đời nào liều mạng vì chuyện này đâu.</t>
+          <t>Gì? Cậu không thấy là chúng ta không phải đối thủ của {Male=him;Female=her} à? Muốn gây sự thì cứ tự nhiên, nhưng tôi không đời nào liều mạng vì chuyện này đâu.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Cậu đúng là không biết ngậm miệng lại, phải không?</t>
+          <t>Mày đúng là không biết ngậm miệng lại, phải không?</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Hả? Sao ngươi cứ nhìn ta thế? Đợi đã, ta đã khai hết những gì ta biết rồi mà! Aaa—</t>
+          <t>Hả? Sao mày cứ nhìn tao thế? Đợi đã, tao đã khai hết những gì tao biết rồi mà! Aaa—</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Ngươi vừa nói cái gì?! Được rồi, ta sẽ đến kho hàng phía bắc ngay bây giờ! Đợi đấy, xem ta vác cả trăm kiện hàng đó… trong một lần luôn!</t>
+          <t>Mày vừa nói cái gì?! Được rồi, tao sẽ đến kho hàng phía bắc ngay bây giờ! Đợi đấy, xem tao vác cả trăm kiện hàng đó… trong một lần luôn!</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ta tưởng cậu đang nói mê trong giấc ngủ...</t>
+          <t>Tao tưởng cậu đang nói mê trong giấc ngủ...</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Cậu tìm đúng người rồi đấy. Thực ra, chính ta là người đầu tiên nhìn thấy mấy thứ quái dị đó.</t>
+          <t>Cậu tìm đúng người rồi đấy. Thực ra, chính tao là người đầu tiên nhìn thấy mấy thứ quái dị đó.</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Cậu muốn gì?</t>
+          <t>Mày muốn gì?</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Cậu thực sự nghĩ là sau khi phá hủy kho hàng và cản trở công việc của chúng ta, chúng ta sẽ để cậu ung dung bỏ đi à?!</t>
+          <t>Cậu thực sự nghĩ là sau khi phá hủy kho hàng và cản trở công việc của chúng tao, chúng tao sẽ để cậu ung dung bỏ đi à?!</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Ồ, hóa ra cậu cũng đến vì tiền à? Nghe này, đưa ra con số đi, chúng ta trả gấp đôi để cậu câm miệng! Thế nào? Nhận tiền rồi biến đi!</t>
+          <t>Ồ, hóa ra cậu cũng đến vì tiền à? Nghe này, đưa ra con số đi, chúng tao trả gấp đôi để cậu câm miệng! Thế nào? Nhận tiền rồi biến đi!</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Vậy thì ngươi muốn gì ở ta nữa hả?!</t>
+          <t>Vậy thì mày muốn gì ở tao nữa hả?!</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Cách ngươi ép buộc mấy họa sĩ... rồi đẩy họ vào chỗ chết chỉ vì lợi nhuận... Ta sẽ phơi bày tất cả!</t>
+          <t>Cách mày ép buộc mấy họa sĩ... rồi đẩy họ vào chỗ chết chỉ vì lợi nhuận... Tao sẽ phơi bày tất cả!</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Ta rất vui khi kỹ năng của mình tiến bộ, nhưng mà...</t>
+          <t>Tao rất vui khi kỹ năng của mình tiến bộ, nhưng mà...</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Làng Tạ Hoa là điểm dừng chân đầu tiên của tôi khi đặt chân đến Kim Châu một mình.</t>
+          <t>Làng Tạ Hoa là điểm dừng chân đầu tiên của tôi khi đặt chân đến Jinzhou một mình.</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Dù ta nghĩ gì, cuối cùng cũng trở thành hiện thực.</t>
+          <t>Dù tao nghĩ gì, cuối cùng cũng trở thành hiện thực.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Ta đã thử vẽ mà không dựa vào năng lực của mình, nhưng…</t>
+          <t>Tao đã thử vẽ mà không dựa vào năng lực của mình, nhưng…</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Ta muốn đến thăm Mingyan. Dù sao thì cô ấy cũng dính líu vào mọi chuyện này, và ta muốn kể cho cô ấy nghe tất cả.</t>
+          <t>Tao muốn đến thăm Mingyan. Dù sao thì cô ấy cũng dính líu vào mọi chuyện này, và tao muốn kể cho cô ấy nghe tất cả.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Vết thương của cậu...</t>
+          <t>Vết thương của bạn...</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Anh biết tôi à?</t>
+          <t>Cậu biết tớ à?</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Và... Ta vẫn còn nợ cậu một lời xin lỗi.</t>
+          <t>Và... Tao vẫn còn nợ cậu một lời xin lỗi.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Hừ. Có lẽ... từ đầu ta đã không sinh ra để làm họa sĩ...</t>
+          <t>Hừ. Có lẽ... từ đầu tao đã không sinh ra để làm họa sĩ...</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Ta nghĩ chắc cô ấy sẽ suy nghĩ về chuyện này.</t>
+          <t>Tao nghĩ chắc cô ấy sẽ suy nghĩ về chuyện này.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ta nghĩ cô ấy đã hiểu ý cậu nói lúc nãy.</t>
+          <t>Tao nghĩ cô ấy đã hiểu ý cậu nói lúc nãy.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Thấy cánh tay ta không? Bọn quái vật xé nát nó rồi.</t>
+          <t>Thấy cánh tay tao không? Bọn quái vật xé nát nó rồi.</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Nhưng ta cá là cô ta đang trốn tránh điều gì đó.</t>
+          <t>Nhưng tao cá là cô ta đang trốn tránh điều gì đó.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Chân ta vẫn còn đau nhức sau chuyến vận chuyển lần trước.</t>
+          <t>Chân tao vẫn còn đau nhức sau chuyến vận chuyển lần trước.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Này, ta đang nghĩ... Chẳng lẽ tụi mình bị giáng chức? Có phải vì thế mà họ đưa tụi mình đến đây không?</t>
+          <t>Này, tao đang nghĩ... Chẳng lẽ tụi mình bị giáng chức? Có phải vì thế mà họ đưa tụi mình đến đây không?</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>R-rover? Bạn're here...:::Rover? Cậu ở đây à...</t>
+          <t>R-rover? You're here...:::Vận Mệnh Giả? Cậu ở đây à...</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Ta không sao. Sao cậu lại ở đây?</t>
+          <t>Tao không sao. Sao cậu lại ở đây?</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Sao ta lại phải xuống kho đếm mấy bức tranh đó lần nữa nhỉ...</t>
+          <t>Sao tao lại phải xuống kho đếm mấy bức tranh đó lần nữa nhỉ...</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ta có liên lạc với một trong những khách hàng của chúng ta hôm nọ…</t>
+          <t>Tao có liên lạc với một trong những khách hàng của chúng ta hôm nọ…</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>May mắn thôi... Nếu không có cha mẹ cầm tay dẫn dắt, ngươi làm gì có được thứ đáng lẽ thuộc về ta!</t>
+          <t>May mắn thôi... Nếu không có cha mẹ cầm tay dẫn dắt, mày làm gì có được thứ đáng lẽ thuộc về tao!</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Cậu đã tạo ra những tuyệt tác mà chính ta cũng ao ước được sáng tác. Táo bạo, phóng khoáng...</t>
+          <t>Cậu đã tạo ra những tuyệt tác mà chính tao cũng ao ước được sáng tác. Táo bạo, phóng khoáng...</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nó thật đẹp.</t>
+          <t>Thật đẹp.</t>
         </is>
       </c>
     </row>
